--- a/Result/profitability/3043.xlsx
+++ b/Result/profitability/3043.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.02</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.23875</v>
+        <v>-0.21625</v>
       </c>
       <c r="N2" t="n">
-        <v>20.2875</v>
+        <v>21.225</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>-0.27</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.305</v>
+        <v>-0.30375</v>
       </c>
       <c r="N3" t="n">
-        <v>19.57125</v>
+        <v>20.14</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.59</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.285</v>
+        <v>-0.26875</v>
       </c>
       <c r="N4" t="n">
-        <v>19.175</v>
+        <v>19.18875</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>-0.55</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.3925000000000001</v>
+        <v>-0.2450000000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>16.975</v>
+        <v>17.09</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.05</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.29375</v>
+        <v>-0.22875</v>
       </c>
       <c r="N6" t="n">
-        <v>15.53375</v>
+        <v>17.67375</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>-0.44</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.3387500000000001</v>
+        <v>-0.01375000000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>16.1375</v>
+        <v>16.395</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.03</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.06500000000000004</v>
+        <v>-0.01625000000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>15.3775</v>
+        <v>15.76625</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1518,7 +1518,7 @@
         <v>-0.47</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.1300000000000001</v>
+        <v>-0.13</v>
       </c>
       <c r="N9" t="n">
         <v>14.8475</v>
@@ -1772,7 +1772,7 @@
         <v>1.13</v>
       </c>
       <c r="M11" t="n">
-        <v>0.06749999999999995</v>
+        <v>0.06749999999999998</v>
       </c>
       <c r="N11" t="n">
         <v>16.585</v>
@@ -9838,6 +9838,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3043</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>256</v>
+      </c>
+      <c r="D75" t="n">
+        <v>190</v>
+      </c>
+      <c r="E75" t="n">
+        <v>67</v>
+      </c>
+      <c r="F75" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="G75" t="n">
+        <v>15</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>5.95%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>3</v>
+      </c>
+      <c r="J75" t="n">
+        <v>19</v>
+      </c>
+      <c r="K75" t="n">
+        <v>17</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.18625</v>
+      </c>
+      <c r="N75" t="n">
+        <v>21.67875</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="X75" t="n">
+        <v>7.799999999999999</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>3.110000000000003</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.1352762070465421</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-1.594594594594595</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>0.9200000000000017</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.03653693407466241</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
